--- a/model/Output_Budget/0. Current Case/Output_0_40.xlsx
+++ b/model/Output_Budget/0. Current Case/Output_0_40.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Output_Budget/0. Current Case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_8EE53270D62EC23918CDE0E8BC4A50FB64E9FEEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAA02AA1-0F30-402D-912F-E82ED2F83C45}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_8EE53270D62EC23918CDE0E8BC4A50FB64E9FEEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11290BC5-0DAD-47B7-BB72-693130BC468D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="69">
   <si>
     <t>Interest Rate</t>
   </si>
@@ -254,11 +254,17 @@
   <si>
     <t>surplus</t>
   </si>
+  <si>
+    <t>CF</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -309,11 +315,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,15 +626,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +645,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -640,7 +653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -648,7 +661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -656,7 +669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -664,7 +677,7 @@
         <v>2275865.281941582</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -672,15 +685,22 @@
         <v>13476767.256909089</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8">
         <v>766877.91654604638</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>-30789066.369910646</v>
+      </c>
+      <c r="D8">
+        <f>B8/C8</f>
+        <v>-2.4907475508757104E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -688,7 +708,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -696,7 +716,7 @@
         <v>6960612.8616873352</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -11358,10 +11378,13 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Z47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="26" max="26" width="11.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
         <v>0</v>
       </c>
@@ -11435,7 +11458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -11511,8 +11534,12 @@
       <c r="Y2">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z2">
+        <f>SUM(B2:Y2)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -11588,8 +11615,12 @@
       <c r="Y3">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z3">
+        <f>SUM(B3:Y3)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -11665,8 +11696,12 @@
       <c r="Y4">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z4">
+        <f>SUM(B4:Y4)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
@@ -11742,8 +11777,12 @@
       <c r="Y5">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z5">
+        <f t="shared" ref="Z5" si="0">SUM(B5:Y5)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -11819,8 +11858,12 @@
       <c r="Y6">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z6">
+        <f t="shared" ref="Z6" si="1">SUM(B6:Y6)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -11896,8 +11939,12 @@
       <c r="Y7">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z7">
+        <f t="shared" ref="Z7" si="2">SUM(B7:Y7)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -11973,8 +12020,12 @@
       <c r="Y8">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z8">
+        <f t="shared" ref="Z8" si="3">SUM(B8:Y8)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
@@ -12050,8 +12101,12 @@
       <c r="Y9">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z9">
+        <f t="shared" ref="Z9" si="4">SUM(B9:Y9)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -12127,8 +12182,12 @@
       <c r="Y10">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z10">
+        <f t="shared" ref="Z10" si="5">SUM(B10:Y10)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -12204,8 +12263,12 @@
       <c r="Y11">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z11">
+        <f t="shared" ref="Z11" si="6">SUM(B11:Y11)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -12281,8 +12344,12 @@
       <c r="Y12">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z12">
+        <f t="shared" ref="Z12" si="7">SUM(B12:Y12)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -12358,8 +12425,12 @@
       <c r="Y13">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z13">
+        <f t="shared" ref="Z13" si="8">SUM(B13:Y13)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -12435,8 +12506,12 @@
       <c r="Y14">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z14">
+        <f t="shared" ref="Z14" si="9">SUM(B14:Y14)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -12512,8 +12587,12 @@
       <c r="Y15">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z15">
+        <f t="shared" ref="Z15" si="10">SUM(B15:Y15)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -12589,8 +12668,12 @@
       <c r="Y16">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z16">
+        <f t="shared" ref="Z16" si="11">SUM(B16:Y16)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -12666,8 +12749,12 @@
       <c r="Y17">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z17">
+        <f t="shared" ref="Z17" si="12">SUM(B17:Y17)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -12743,8 +12830,12 @@
       <c r="Y18">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z18">
+        <f t="shared" ref="Z18" si="13">SUM(B18:Y18)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -12820,8 +12911,12 @@
       <c r="Y19">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z19">
+        <f t="shared" ref="Z19" si="14">SUM(B19:Y19)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -12897,8 +12992,12 @@
       <c r="Y20">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z20">
+        <f t="shared" ref="Z20" si="15">SUM(B20:Y20)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -12974,8 +13073,12 @@
       <c r="Y21">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z21">
+        <f t="shared" ref="Z21" si="16">SUM(B21:Y21)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -13051,8 +13154,12 @@
       <c r="Y22">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z22">
+        <f t="shared" ref="Z22" si="17">SUM(B22:Y22)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>43</v>
       </c>
@@ -13128,8 +13235,12 @@
       <c r="Y23">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z23">
+        <f t="shared" ref="Z23" si="18">SUM(B23:Y23)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
@@ -13205,8 +13316,12 @@
       <c r="Y24">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z24">
+        <f t="shared" ref="Z24" si="19">SUM(B24:Y24)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
@@ -13282,8 +13397,12 @@
       <c r="Y25">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z25">
+        <f t="shared" ref="Z25" si="20">SUM(B25:Y25)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
@@ -13359,8 +13478,12 @@
       <c r="Y26">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z26">
+        <f t="shared" ref="Z26" si="21">SUM(B26:Y26)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -13436,8 +13559,12 @@
       <c r="Y27">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z27">
+        <f t="shared" ref="Z27" si="22">SUM(B27:Y27)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -13513,8 +13640,12 @@
       <c r="Y28">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z28">
+        <f t="shared" ref="Z28" si="23">SUM(B28:Y28)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
@@ -13590,8 +13721,12 @@
       <c r="Y29">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z29">
+        <f t="shared" ref="Z29" si="24">SUM(B29:Y29)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>50</v>
       </c>
@@ -13667,8 +13802,12 @@
       <c r="Y30">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z30">
+        <f t="shared" ref="Z30" si="25">SUM(B30:Y30)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
@@ -13744,8 +13883,12 @@
       <c r="Y31">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z31">
+        <f t="shared" ref="Z31" si="26">SUM(B31:Y31)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
@@ -13821,8 +13964,12 @@
       <c r="Y32">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z32">
+        <f t="shared" ref="Z32" si="27">SUM(B32:Y32)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
@@ -13898,8 +14045,12 @@
       <c r="Y33">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z33">
+        <f t="shared" ref="Z33" si="28">SUM(B33:Y33)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -13975,8 +14126,12 @@
       <c r="Y34">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z34">
+        <f t="shared" ref="Z34" si="29">SUM(B34:Y34)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -14052,8 +14207,12 @@
       <c r="Y35">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z35">
+        <f t="shared" ref="Z35" si="30">SUM(B35:Y35)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>56</v>
       </c>
@@ -14129,8 +14288,12 @@
       <c r="Y36">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z36">
+        <f t="shared" ref="Z36" si="31">SUM(B36:Y36)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
@@ -14206,8 +14369,12 @@
       <c r="Y37">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z37">
+        <f t="shared" ref="Z37" si="32">SUM(B37:Y37)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>58</v>
       </c>
@@ -14283,8 +14450,12 @@
       <c r="Y38">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z38">
+        <f t="shared" ref="Z38" si="33">SUM(B38:Y38)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>59</v>
       </c>
@@ -14360,8 +14531,12 @@
       <c r="Y39">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z39">
+        <f t="shared" ref="Z39" si="34">SUM(B39:Y39)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
@@ -14437,8 +14612,12 @@
       <c r="Y40">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z40">
+        <f t="shared" ref="Z40" si="35">SUM(B40:Y40)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>61</v>
       </c>
@@ -14514,8 +14693,12 @@
       <c r="Y41">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z41">
+        <f t="shared" ref="Z41" si="36">SUM(B41:Y41)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>62</v>
       </c>
@@ -14591,8 +14774,12 @@
       <c r="Y42">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z42">
+        <f t="shared" ref="Z42" si="37">SUM(B42:Y42)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>63</v>
       </c>
@@ -14668,8 +14855,12 @@
       <c r="Y43">
         <v>-218.58465335209479</v>
       </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z43">
+        <f t="shared" ref="Z43" si="38">SUM(B43:Y43)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>64</v>
       </c>
@@ -14745,8 +14936,12 @@
       <c r="Y44">
         <v>-386.23793865605359</v>
       </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z44">
+        <f t="shared" ref="Z44" si="39">SUM(B44:Y44)*199</f>
+        <v>-1386842.4148154764</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>65</v>
       </c>
@@ -14822,8 +15017,12 @@
       <c r="Y45">
         <v>-205.68269577730439</v>
       </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z45">
+        <f t="shared" ref="Z45" si="40">SUM(B45:Y45)*106</f>
+        <v>-410345.50791745115</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>66</v>
       </c>
@@ -14898,6 +15097,16 @@
       </c>
       <c r="Y46">
         <v>-218.58465335209479</v>
+      </c>
+      <c r="Z46">
+        <f t="shared" ref="Z46" si="41">SUM(B46:Y46)*60</f>
+        <v>-255416.50192778069</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="Z47">
+        <f>SUM(Z2:Z46)</f>
+        <v>-30789066.369910646</v>
       </c>
     </row>
   </sheetData>
@@ -26027,8 +26236,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
@@ -26226,6 +26438,9 @@
       <c r="P4">
         <v>0</v>
       </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26234,8 +26449,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
@@ -26432,6 +26650,77 @@
       </c>
       <c r="P4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6">
+        <f>800*B2</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:P6" si="0">800*C2</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>262201.80677610793</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>21544.62652043844</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>8471.8801202596715</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>232185.30013540987</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>51561.13316113656</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>21797.862761263055</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>183601.7438940632</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B7" s="3">
+        <f>NPV(0.1,C6:P6)</f>
+        <v>408741.75391013426</v>
       </c>
     </row>
   </sheetData>
